--- a/artfynd/A 56621-2024 artfynd.xlsx
+++ b/artfynd/A 56621-2024 artfynd.xlsx
@@ -5910,7 +5910,7 @@
         <v>0</v>
       </c>
       <c r="AE48" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG48" t="b">
         <v>0</v>

--- a/artfynd/A 56621-2024 artfynd.xlsx
+++ b/artfynd/A 56621-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY78"/>
+  <dimension ref="A1:AY84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>115983111</v>
+        <v>115983150</v>
       </c>
       <c r="B2" t="n">
-        <v>90624</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83299</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>658</v>
+        <v>308</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>532603</v>
+        <v>532782</v>
       </c>
       <c r="R2" t="n">
-        <v>7238482</v>
+        <v>7238438</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -764,7 +759,7 @@
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>5581</t>
+          <t>5676</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -775,7 +770,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Robin Karlsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -786,15 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>115983280</v>
+        <v>115983257</v>
       </c>
       <c r="B3" t="n">
-        <v>82248</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83299</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -802,21 +792,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1312</v>
+        <v>308</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -826,10 +816,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>532573</v>
+        <v>532372</v>
       </c>
       <c r="R3" t="n">
-        <v>7238303</v>
+        <v>7238323</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -875,7 +865,7 @@
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>5606</t>
+          <t>5523</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -886,7 +876,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Robin Karlsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -897,37 +887,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>115983257</v>
+        <v>115983127</v>
       </c>
       <c r="B4" t="n">
-        <v>74640</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78350</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>308</v>
+        <v>314</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -937,10 +922,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>532372</v>
+        <v>532766</v>
       </c>
       <c r="R4" t="n">
-        <v>7238323</v>
+        <v>7238464</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -986,7 +971,7 @@
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>5523</t>
+          <t>5652</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1008,19 +993,14 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>115983226</v>
+        <v>115983178</v>
       </c>
       <c r="B5" t="n">
-        <v>77463</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78350</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1048,10 +1028,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>532753</v>
+        <v>532442</v>
       </c>
       <c r="R5" t="n">
-        <v>7238342</v>
+        <v>7238385</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1097,7 +1077,7 @@
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>5683</t>
+          <t>5584</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1108,7 +1088,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Robin Karlsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1119,37 +1099,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>115983119</v>
+        <v>115983200</v>
       </c>
       <c r="B6" t="n">
-        <v>79559</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78350</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2081</v>
+        <v>314</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1159,10 +1134,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>532262</v>
+        <v>532421</v>
       </c>
       <c r="R6" t="n">
-        <v>7238471</v>
+        <v>7238362</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1208,7 +1183,7 @@
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>5471</t>
+          <t>5571</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1219,7 +1194,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Robin Karlsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1230,37 +1205,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>115983117</v>
+        <v>115983217</v>
       </c>
       <c r="B7" t="n">
-        <v>79464</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78350</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6456</v>
+        <v>314</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1270,10 +1240,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>532261</v>
+        <v>532354</v>
       </c>
       <c r="R7" t="n">
-        <v>7238472</v>
+        <v>7238346</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1319,7 +1289,7 @@
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>5480</t>
+          <t>5513</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1330,7 +1300,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Robin Karlsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1341,19 +1311,14 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>115983270</v>
+        <v>115983226</v>
       </c>
       <c r="B8" t="n">
-        <v>77463</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78350</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1381,10 +1346,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>532365</v>
+        <v>532753</v>
       </c>
       <c r="R8" t="n">
-        <v>7238310</v>
+        <v>7238342</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1430,7 +1395,7 @@
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>5534</t>
+          <t>5683</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1441,7 +1406,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Robin Karlsson</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1452,37 +1417,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>115983195</v>
+        <v>115983270</v>
       </c>
       <c r="B9" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78350</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>314</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1492,10 +1452,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>532520</v>
+        <v>532365</v>
       </c>
       <c r="R9" t="n">
-        <v>7238364</v>
+        <v>7238310</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1541,7 +1501,7 @@
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>5600</t>
+          <t>5534</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1563,37 +1523,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>115983110</v>
+        <v>115983232</v>
       </c>
       <c r="B10" t="n">
-        <v>79587</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83298</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6462</v>
+        <v>492</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1603,10 +1558,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>532415</v>
+        <v>532754</v>
       </c>
       <c r="R10" t="n">
-        <v>7238485</v>
+        <v>7238340</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1645,14 +1600,14 @@
         <v>0</v>
       </c>
       <c r="AE10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>5533</t>
+          <t>5681</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1663,7 +1618,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Robin Karlsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1674,37 +1629,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>115983155</v>
+        <v>115983111</v>
       </c>
       <c r="B11" t="n">
-        <v>79587</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6462</v>
+        <v>658</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1714,10 +1664,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>532308</v>
+        <v>532603</v>
       </c>
       <c r="R11" t="n">
-        <v>7238431</v>
+        <v>7238482</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1763,7 +1713,7 @@
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>5504</t>
+          <t>5581</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1785,15 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>115983267</v>
+        <v>115983192</v>
       </c>
       <c r="B12" t="n">
-        <v>90359</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1801,21 +1746,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>864</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1825,10 +1770,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>532378</v>
+        <v>532306</v>
       </c>
       <c r="R12" t="n">
-        <v>7238313</v>
+        <v>7238366</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1874,7 +1819,7 @@
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>5535</t>
+          <t>5492</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -1896,37 +1841,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>115983116</v>
+        <v>115983108</v>
       </c>
       <c r="B13" t="n">
-        <v>79594</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6464</v>
+        <v>1312</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1936,10 +1876,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>532258</v>
+        <v>532603</v>
       </c>
       <c r="R13" t="n">
-        <v>7238473</v>
+        <v>7238491</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1985,7 +1925,7 @@
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>5472</t>
+          <t>5582</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2007,37 +1947,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>115983210</v>
+        <v>115983128</v>
       </c>
       <c r="B14" t="n">
-        <v>97680</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221952</v>
+        <v>1312</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2047,10 +1982,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>532582</v>
+        <v>532467</v>
       </c>
       <c r="R14" t="n">
-        <v>7238354</v>
+        <v>7238464</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2096,7 +2031,7 @@
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>5590</t>
+          <t>5556</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2118,15 +2053,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>115983234</v>
+        <v>115983147</v>
       </c>
       <c r="B15" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2134,39 +2064,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Dikanäs - Kittelfjäll, Ås lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>532407</v>
+        <v>532721</v>
       </c>
       <c r="R15" t="n">
-        <v>7238340</v>
+        <v>7238441</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2201,11 +2126,6 @@
           <t>2023-06-15</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Hackade hål</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2217,7 +2137,7 @@
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>5566</t>
+          <t>5659</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2228,7 +2148,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Robin Karlsson</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
@@ -2239,15 +2159,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>115983113</v>
+        <v>115983160</v>
       </c>
       <c r="B16" t="n">
-        <v>90359</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2255,21 +2170,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>1312</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2279,10 +2194,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>532405</v>
+        <v>532385</v>
       </c>
       <c r="R16" t="n">
-        <v>7238477</v>
+        <v>7238423</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2328,7 +2243,7 @@
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>5532</t>
+          <t>5519</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2350,37 +2265,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>115983170</v>
+        <v>115983163</v>
       </c>
       <c r="B17" t="n">
-        <v>79593</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6463</v>
+        <v>1312</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2390,10 +2300,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>532773</v>
+        <v>532769</v>
       </c>
       <c r="R17" t="n">
-        <v>7238405</v>
+        <v>7238421</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2439,7 +2349,7 @@
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>5669</t>
+          <t>5657</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2461,54 +2371,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>115983260</v>
+        <v>115983280</v>
       </c>
       <c r="B18" t="n">
-        <v>57372</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103031</v>
+        <v>1312</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Dikanäs - Kittelfjäll, Ås lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>532549</v>
+        <v>532573</v>
       </c>
       <c r="R18" t="n">
-        <v>7238321</v>
+        <v>7238303</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2554,7 +2455,7 @@
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>5608</t>
+          <t>5606</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2565,7 +2466,7 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Robin Karlsson</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
@@ -2576,54 +2477,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>115983263</v>
+        <v>115983105</v>
       </c>
       <c r="B19" t="n">
-        <v>97576</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83312</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>219790</v>
+        <v>1467</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Dikanäs - Kittelfjäll, Ås lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>532380</v>
+        <v>532272</v>
       </c>
       <c r="R19" t="n">
-        <v>7238319</v>
+        <v>7238493</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2669,7 +2561,7 @@
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>5543</t>
+          <t>5479</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2680,7 +2572,7 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Robin Karlsson</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
@@ -2691,37 +2583,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>115983107</v>
+        <v>115983122</v>
       </c>
       <c r="B20" t="n">
-        <v>93496</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83312</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1004672</v>
+        <v>1467</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Källmossor</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Philonotis</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Brid.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2731,10 +2618,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>532686</v>
+        <v>532762</v>
       </c>
       <c r="R20" t="n">
-        <v>7238492</v>
+        <v>7238470</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2780,7 +2667,7 @@
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>5632</t>
+          <t>5647</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -2802,15 +2689,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>115983134</v>
+        <v>115983148</v>
       </c>
       <c r="B21" t="n">
-        <v>79559</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83312</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2818,21 +2700,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2081</v>
+        <v>1467</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2842,10 +2724,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>532506</v>
+        <v>532375</v>
       </c>
       <c r="R21" t="n">
-        <v>7238452</v>
+        <v>7238441</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2891,7 +2773,7 @@
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>5559</t>
+          <t>5517</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -2913,37 +2795,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>115983275</v>
+        <v>115983152</v>
       </c>
       <c r="B22" t="n">
-        <v>94068</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83312</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2809</v>
+        <v>1467</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2953,10 +2830,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>532367</v>
+        <v>532389</v>
       </c>
       <c r="R22" t="n">
-        <v>7238306</v>
+        <v>7238434</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3002,7 +2879,7 @@
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>5525</t>
+          <t>5518</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3013,7 +2890,7 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Robin Karlsson</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
@@ -3024,15 +2901,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>115983220</v>
+        <v>115983161</v>
       </c>
       <c r="B23" t="n">
-        <v>90359</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83312</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3040,21 +2912,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5432</v>
+        <v>1467</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3064,10 +2936,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>532728</v>
+        <v>532256</v>
       </c>
       <c r="R23" t="n">
-        <v>7238345</v>
+        <v>7238423</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3113,7 +2985,7 @@
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>5685</t>
+          <t>5488</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3135,15 +3007,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>115983154</v>
+        <v>115983104</v>
       </c>
       <c r="B24" t="n">
-        <v>79559</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3175,10 +3042,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>532317</v>
+        <v>532278</v>
       </c>
       <c r="R24" t="n">
-        <v>7238431</v>
+        <v>7238499</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3224,7 +3091,7 @@
       </c>
       <c r="AR24" t="inlineStr">
         <is>
-          <t>5503</t>
+          <t>5494</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3246,15 +3113,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>115983148</v>
+        <v>115983114</v>
       </c>
       <c r="B25" t="n">
-        <v>74652</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3262,21 +3124,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1467</v>
+        <v>2081</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3286,10 +3148,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>532375</v>
+        <v>532261</v>
       </c>
       <c r="R25" t="n">
-        <v>7238441</v>
+        <v>7238474</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3335,7 +3197,7 @@
       </c>
       <c r="AR25" t="inlineStr">
         <is>
-          <t>5517</t>
+          <t>5481</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3357,15 +3219,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>115983217</v>
+        <v>115983118</v>
       </c>
       <c r="B26" t="n">
-        <v>77463</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3373,21 +3230,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>314</v>
+        <v>2081</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3397,10 +3254,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>532354</v>
+        <v>532293</v>
       </c>
       <c r="R26" t="n">
-        <v>7238346</v>
+        <v>7238471</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3446,7 +3303,7 @@
       </c>
       <c r="AR26" t="inlineStr">
         <is>
-          <t>5513</t>
+          <t>5495</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3457,7 +3314,7 @@
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Robin Karlsson</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
@@ -3468,15 +3325,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>115983171</v>
+        <v>115983119</v>
       </c>
       <c r="B27" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3484,39 +3336,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Dikanäs - Kittelfjäll, Ås lm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>532453</v>
+        <v>532262</v>
       </c>
       <c r="R27" t="n">
-        <v>7238403</v>
+        <v>7238471</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3551,11 +3398,6 @@
           <t>2023-06-15</t>
         </is>
       </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Hackade i gran</t>
-        </is>
-      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
@@ -3567,7 +3409,7 @@
       </c>
       <c r="AR27" t="inlineStr">
         <is>
-          <t>5586</t>
+          <t>5471</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3578,7 +3420,7 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Robin Karlsson</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
@@ -3589,15 +3431,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>115983153</v>
+        <v>115983126</v>
       </c>
       <c r="B28" t="n">
-        <v>90359</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3605,21 +3442,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3629,10 +3466,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>532761</v>
+        <v>532509</v>
       </c>
       <c r="R28" t="n">
-        <v>7238433</v>
+        <v>7238466</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3678,7 +3515,7 @@
       </c>
       <c r="AR28" t="inlineStr">
         <is>
-          <t>5656</t>
+          <t>5557</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -3700,15 +3537,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>115983216</v>
+        <v>115983134</v>
       </c>
       <c r="B29" t="n">
-        <v>74647</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3716,21 +3548,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6440</v>
+        <v>2081</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3740,10 +3572,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>532758</v>
+        <v>532506</v>
       </c>
       <c r="R29" t="n">
-        <v>7238346</v>
+        <v>7238452</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3789,7 +3621,7 @@
       </c>
       <c r="AR29" t="inlineStr">
         <is>
-          <t>5682</t>
+          <t>5559</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -3811,15 +3643,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>115983163</v>
+        <v>115983142</v>
       </c>
       <c r="B30" t="n">
-        <v>82248</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3827,21 +3654,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1312</v>
+        <v>2081</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3851,10 +3678,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>532769</v>
+        <v>532370</v>
       </c>
       <c r="R30" t="n">
-        <v>7238421</v>
+        <v>7238443</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3900,7 +3727,7 @@
       </c>
       <c r="AR30" t="inlineStr">
         <is>
-          <t>5657</t>
+          <t>5505</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -3922,37 +3749,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>115983141</v>
+        <v>115983154</v>
       </c>
       <c r="B31" t="n">
-        <v>79594</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6464</v>
+        <v>2081</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3962,10 +3784,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>532722</v>
+        <v>532317</v>
       </c>
       <c r="R31" t="n">
-        <v>7238444</v>
+        <v>7238431</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4011,7 +3833,7 @@
       </c>
       <c r="AR31" t="inlineStr">
         <is>
-          <t>5660</t>
+          <t>5503</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4033,37 +3855,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>115983130</v>
+        <v>115983159</v>
       </c>
       <c r="B32" t="n">
-        <v>79594</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6464</v>
+        <v>2081</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4073,10 +3890,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>532509</v>
+        <v>532516</v>
       </c>
       <c r="R32" t="n">
-        <v>7238456</v>
+        <v>7238424</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4122,7 +3939,7 @@
       </c>
       <c r="AR32" t="inlineStr">
         <is>
-          <t>5558</t>
+          <t>5561</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4144,37 +3961,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>115983136</v>
+        <v>115983183</v>
       </c>
       <c r="B33" t="n">
-        <v>79593</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6463</v>
+        <v>2081</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4184,10 +3996,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>532509</v>
+        <v>532617</v>
       </c>
       <c r="R33" t="n">
-        <v>7238450</v>
+        <v>7238375</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4233,7 +4045,7 @@
       </c>
       <c r="AR33" t="inlineStr">
         <is>
-          <t>5560</t>
+          <t>5589</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4255,15 +4067,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>115983223</v>
+        <v>115983138</v>
       </c>
       <c r="B34" t="n">
-        <v>79524</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96338</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4271,21 +4078,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>229748</v>
+        <v>2809</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4295,10 +4102,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>532755</v>
+        <v>532780</v>
       </c>
       <c r="R34" t="n">
-        <v>7238343</v>
+        <v>7238445</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4344,7 +4151,7 @@
       </c>
       <c r="AR34" t="inlineStr">
         <is>
-          <t>5680</t>
+          <t>5671</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4355,7 +4162,7 @@
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Robin Karlsson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr">
@@ -4366,37 +4173,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>115983201</v>
+        <v>115983254</v>
       </c>
       <c r="B35" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96338</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>2809</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4406,10 +4208,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>532422</v>
+        <v>532594</v>
       </c>
       <c r="R35" t="n">
-        <v>7238361</v>
+        <v>7238326</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4455,7 +4257,7 @@
       </c>
       <c r="AR35" t="inlineStr">
         <is>
-          <t>5573</t>
+          <t>5613</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -4477,15 +4279,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>115983125</v>
+        <v>115983275</v>
       </c>
       <c r="B36" t="n">
-        <v>79587</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96338</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4493,21 +4290,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6462</v>
+        <v>2809</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4517,10 +4314,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>532454</v>
+        <v>532367</v>
       </c>
       <c r="R36" t="n">
-        <v>7238467</v>
+        <v>7238306</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4566,7 +4363,7 @@
       </c>
       <c r="AR36" t="inlineStr">
         <is>
-          <t>5541</t>
+          <t>5525</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -4577,7 +4374,7 @@
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Robin Karlsson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr">
@@ -4588,37 +4385,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>115983180</v>
+        <v>115983187</v>
       </c>
       <c r="B37" t="n">
-        <v>79587</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4628,10 +4420,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>532514</v>
+        <v>532329</v>
       </c>
       <c r="R37" t="n">
-        <v>7238380</v>
+        <v>7238371</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4677,7 +4469,7 @@
       </c>
       <c r="AR37" t="inlineStr">
         <is>
-          <t>5578</t>
+          <t>5497</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -4688,7 +4480,7 @@
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Robin Karlsson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr">
@@ -4699,37 +4491,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>115983152</v>
+        <v>115983195</v>
       </c>
       <c r="B38" t="n">
-        <v>74652</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1467</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4739,10 +4526,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>532389</v>
+        <v>532520</v>
       </c>
       <c r="R38" t="n">
-        <v>7238434</v>
+        <v>7238364</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4788,7 +4575,7 @@
       </c>
       <c r="AR38" t="inlineStr">
         <is>
-          <t>5518</t>
+          <t>5600</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -4799,7 +4586,7 @@
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Robin Karlsson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr">
@@ -4810,37 +4597,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>115983168</v>
+        <v>115983201</v>
       </c>
       <c r="B39" t="n">
-        <v>79587</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4850,10 +4632,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>532775</v>
+        <v>532422</v>
       </c>
       <c r="R39" t="n">
-        <v>7238405</v>
+        <v>7238361</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4899,7 +4681,7 @@
       </c>
       <c r="AR39" t="inlineStr">
         <is>
-          <t>5670</t>
+          <t>5573</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -4910,7 +4692,7 @@
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Robin Karlsson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr">
@@ -4921,37 +4703,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>115983103</v>
+        <v>115983268</v>
       </c>
       <c r="B40" t="n">
-        <v>79594</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4961,10 +4738,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>532279</v>
+        <v>532366</v>
       </c>
       <c r="R40" t="n">
-        <v>7238500</v>
+        <v>7238311</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -5010,7 +4787,7 @@
       </c>
       <c r="AR40" t="inlineStr">
         <is>
-          <t>5493</t>
+          <t>5529</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5021,7 +4798,7 @@
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Robin Karlsson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr">
@@ -5032,37 +4809,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>115983114</v>
+        <v>115983121</v>
       </c>
       <c r="B41" t="n">
-        <v>79559</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83290</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>2081</v>
+        <v>6439</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5072,10 +4844,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>532261</v>
+        <v>532764</v>
       </c>
       <c r="R41" t="n">
-        <v>7238474</v>
+        <v>7238470</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5121,7 +4893,7 @@
       </c>
       <c r="AR41" t="inlineStr">
         <is>
-          <t>5481</t>
+          <t>5645</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5132,7 +4904,7 @@
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Robin Karlsson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr">
@@ -5143,37 +4915,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>115983268</v>
+        <v>115983281</v>
       </c>
       <c r="B42" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83290</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>6439</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5183,10 +4950,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>532366</v>
+        <v>532363</v>
       </c>
       <c r="R42" t="n">
-        <v>7238311</v>
+        <v>7238303</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5232,7 +4999,7 @@
       </c>
       <c r="AR42" t="inlineStr">
         <is>
-          <t>5529</t>
+          <t>5526</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -5254,59 +5021,45 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>115983265</v>
+        <v>115983123</v>
       </c>
       <c r="B43" t="n">
-        <v>57372</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>103031</v>
+        <v>6440</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L43" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Dikanäs - Kittelfjäll, Ås lm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>532596</v>
+        <v>532761</v>
       </c>
       <c r="R43" t="n">
-        <v>7238317</v>
+        <v>7238467</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5352,7 +5105,7 @@
       </c>
       <c r="AR43" t="inlineStr">
         <is>
-          <t>5607</t>
+          <t>5644</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -5363,7 +5116,7 @@
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Robin Karlsson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr">
@@ -5374,15 +5127,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>115983137</v>
+        <v>115983124</v>
       </c>
       <c r="B44" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5390,39 +5138,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Dikanäs - Kittelfjäll, Ås lm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>532259</v>
+        <v>532458</v>
       </c>
       <c r="R44" t="n">
-        <v>7238450</v>
+        <v>7238467</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5457,11 +5200,6 @@
           <t>2023-06-15</t>
         </is>
       </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>hackmärken</t>
-        </is>
-      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
@@ -5473,7 +5211,7 @@
       </c>
       <c r="AR44" t="inlineStr">
         <is>
-          <t>5487</t>
+          <t>5542</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -5495,15 +5233,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>115983190</v>
+        <v>115983176</v>
       </c>
       <c r="B45" t="n">
-        <v>74647</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5535,10 +5268,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>532330</v>
+        <v>532531</v>
       </c>
       <c r="R45" t="n">
-        <v>7238368</v>
+        <v>7238388</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5584,7 +5317,7 @@
       </c>
       <c r="AR45" t="inlineStr">
         <is>
-          <t>5496</t>
+          <t>5579</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -5595,7 +5328,7 @@
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Robin Karlsson</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr">
@@ -5606,37 +5339,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>115983281</v>
+        <v>115983190</v>
       </c>
       <c r="B46" t="n">
-        <v>74632</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6439</v>
+        <v>6440</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5646,10 +5374,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>532363</v>
+        <v>532330</v>
       </c>
       <c r="R46" t="n">
-        <v>7238303</v>
+        <v>7238368</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5695,7 +5423,7 @@
       </c>
       <c r="AR46" t="inlineStr">
         <is>
-          <t>5526</t>
+          <t>5496</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -5717,15 +5445,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>115983161</v>
+        <v>115983205</v>
       </c>
       <c r="B47" t="n">
-        <v>74652</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5733,21 +5456,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1467</v>
+        <v>6440</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5757,10 +5480,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>532256</v>
+        <v>532448</v>
       </c>
       <c r="R47" t="n">
-        <v>7238423</v>
+        <v>7238357</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5806,7 +5529,7 @@
       </c>
       <c r="AR47" t="inlineStr">
         <is>
-          <t>5488</t>
+          <t>5595</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -5828,37 +5551,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>115983232</v>
+        <v>115983216</v>
       </c>
       <c r="B48" t="n">
-        <v>74639</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>492</v>
+        <v>6440</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5868,10 +5586,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>532754</v>
+        <v>532758</v>
       </c>
       <c r="R48" t="n">
-        <v>7238340</v>
+        <v>7238346</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5910,14 +5628,14 @@
         <v>0</v>
       </c>
       <c r="AE48" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
       <c r="AR48" t="inlineStr">
         <is>
-          <t>5681</t>
+          <t>5682</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -5928,7 +5646,7 @@
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Robin Karlsson</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr">
@@ -5939,15 +5657,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>115983105</v>
+        <v>115983221</v>
       </c>
       <c r="B49" t="n">
-        <v>74652</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5955,21 +5668,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1467</v>
+        <v>6440</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5979,10 +5692,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>532272</v>
+        <v>532353</v>
       </c>
       <c r="R49" t="n">
-        <v>7238493</v>
+        <v>7238344</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -6028,7 +5741,7 @@
       </c>
       <c r="AR49" t="inlineStr">
         <is>
-          <t>5479</t>
+          <t>5515</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -6039,7 +5752,7 @@
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Robin Karlsson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr">
@@ -6050,15 +5763,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>115983142</v>
+        <v>115983278</v>
       </c>
       <c r="B50" t="n">
-        <v>79559</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6066,21 +5774,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>2081</v>
+        <v>6440</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6090,10 +5798,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>532370</v>
+        <v>532364</v>
       </c>
       <c r="R50" t="n">
-        <v>7238443</v>
+        <v>7238306</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -6139,7 +5847,7 @@
       </c>
       <c r="AR50" t="inlineStr">
         <is>
-          <t>5505</t>
+          <t>5547</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -6150,7 +5858,7 @@
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Robin Karlsson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr">
@@ -6161,37 +5869,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>115983200</v>
+        <v>115983117</v>
       </c>
       <c r="B51" t="n">
-        <v>77463</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80336</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>314</v>
+        <v>6456</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6201,10 +5904,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>532421</v>
+        <v>532261</v>
       </c>
       <c r="R51" t="n">
-        <v>7238362</v>
+        <v>7238472</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6250,7 +5953,7 @@
       </c>
       <c r="AR51" t="inlineStr">
         <is>
-          <t>5571</t>
+          <t>5480</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -6261,7 +5964,7 @@
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Robin Karlsson</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr">
@@ -6272,55 +5975,45 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>115983181</v>
+        <v>115983110</v>
       </c>
       <c r="B52" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Dikanäs - Kittelfjäll, Ås lm</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>532433</v>
+        <v>532415</v>
       </c>
       <c r="R52" t="n">
-        <v>7238380</v>
+        <v>7238485</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6355,11 +6048,6 @@
           <t>2023-06-15</t>
         </is>
       </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Hackade i gran</t>
-        </is>
-      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
@@ -6371,7 +6059,7 @@
       </c>
       <c r="AR52" t="inlineStr">
         <is>
-          <t>5580</t>
+          <t>5533</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -6382,7 +6070,7 @@
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Robin Karlsson</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr">
@@ -6393,15 +6081,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>115983167</v>
+        <v>115983125</v>
       </c>
       <c r="B53" t="n">
-        <v>97680</v>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6409,21 +6092,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>221952</v>
+        <v>6462</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6433,10 +6116,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>532451</v>
+        <v>532454</v>
       </c>
       <c r="R53" t="n">
-        <v>7238409</v>
+        <v>7238467</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6482,7 +6165,7 @@
       </c>
       <c r="AR53" t="inlineStr">
         <is>
-          <t>5593</t>
+          <t>5541</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -6504,37 +6187,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>115983118</v>
+        <v>115983143</v>
       </c>
       <c r="B54" t="n">
-        <v>79559</v>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6544,10 +6222,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>532293</v>
+        <v>532365</v>
       </c>
       <c r="R54" t="n">
-        <v>7238471</v>
+        <v>7238443</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6593,7 +6271,7 @@
       </c>
       <c r="AR54" t="inlineStr">
         <is>
-          <t>5495</t>
+          <t>5506</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -6615,37 +6293,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>115983104</v>
+        <v>115983155</v>
       </c>
       <c r="B55" t="n">
-        <v>79559</v>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6655,10 +6328,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>532278</v>
+        <v>532308</v>
       </c>
       <c r="R55" t="n">
-        <v>7238499</v>
+        <v>7238431</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6704,7 +6377,7 @@
       </c>
       <c r="AR55" t="inlineStr">
         <is>
-          <t>5494</t>
+          <t>5504</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -6726,37 +6399,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>115983128</v>
+        <v>115983168</v>
       </c>
       <c r="B56" t="n">
-        <v>82248</v>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1312</v>
+        <v>6462</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6766,10 +6434,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>532467</v>
+        <v>532775</v>
       </c>
       <c r="R56" t="n">
-        <v>7238464</v>
+        <v>7238405</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6815,7 +6483,7 @@
       </c>
       <c r="AR56" t="inlineStr">
         <is>
-          <t>5556</t>
+          <t>5670</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>
@@ -6837,37 +6505,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>115983160</v>
+        <v>115983180</v>
       </c>
       <c r="B57" t="n">
-        <v>82248</v>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1312</v>
+        <v>6462</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6877,10 +6540,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>532385</v>
+        <v>532514</v>
       </c>
       <c r="R57" t="n">
-        <v>7238423</v>
+        <v>7238380</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6926,7 +6589,7 @@
       </c>
       <c r="AR57" t="inlineStr">
         <is>
-          <t>5519</t>
+          <t>5578</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr"/>
@@ -6948,37 +6611,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>115983183</v>
+        <v>115983253</v>
       </c>
       <c r="B58" t="n">
-        <v>79559</v>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6988,10 +6646,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>532617</v>
+        <v>532388</v>
       </c>
       <c r="R58" t="n">
-        <v>7238375</v>
+        <v>7238330</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -7037,7 +6695,7 @@
       </c>
       <c r="AR58" t="inlineStr">
         <is>
-          <t>5589</t>
+          <t>5555</t>
         </is>
       </c>
       <c r="AT58" t="inlineStr"/>
@@ -7048,7 +6706,7 @@
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Robin Karlsson</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr">
@@ -7059,37 +6717,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>115983126</v>
+        <v>115983136</v>
       </c>
       <c r="B59" t="n">
-        <v>79559</v>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80467</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>2081</v>
+        <v>6463</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7102,7 +6755,7 @@
         <v>532509</v>
       </c>
       <c r="R59" t="n">
-        <v>7238466</v>
+        <v>7238450</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -7148,7 +6801,7 @@
       </c>
       <c r="AR59" t="inlineStr">
         <is>
-          <t>5557</t>
+          <t>5560</t>
         </is>
       </c>
       <c r="AT59" t="inlineStr"/>
@@ -7170,37 +6823,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>115983205</v>
+        <v>115983156</v>
       </c>
       <c r="B60" t="n">
-        <v>74647</v>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80467</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6440</v>
+        <v>6463</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7210,10 +6858,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>532448</v>
+        <v>532400</v>
       </c>
       <c r="R60" t="n">
-        <v>7238357</v>
+        <v>7238430</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -7259,7 +6907,7 @@
       </c>
       <c r="AR60" t="inlineStr">
         <is>
-          <t>5595</t>
+          <t>5531</t>
         </is>
       </c>
       <c r="AT60" t="inlineStr"/>
@@ -7281,37 +6929,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>115983165</v>
+        <v>115983170</v>
       </c>
       <c r="B61" t="n">
-        <v>90359</v>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80467</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>5432</v>
+        <v>6463</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7321,10 +6964,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>532753</v>
+        <v>532773</v>
       </c>
       <c r="R61" t="n">
-        <v>7238419</v>
+        <v>7238405</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7370,7 +7013,7 @@
       </c>
       <c r="AR61" t="inlineStr">
         <is>
-          <t>5658</t>
+          <t>5669</t>
         </is>
       </c>
       <c r="AT61" t="inlineStr"/>
@@ -7392,37 +7035,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>115983108</v>
+        <v>115983229</v>
       </c>
       <c r="B62" t="n">
-        <v>82248</v>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80467</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1312</v>
+        <v>6463</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7432,10 +7070,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>532603</v>
+        <v>532748</v>
       </c>
       <c r="R62" t="n">
-        <v>7238491</v>
+        <v>7238341</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -7481,7 +7119,7 @@
       </c>
       <c r="AR62" t="inlineStr">
         <is>
-          <t>5582</t>
+          <t>5684</t>
         </is>
       </c>
       <c r="AT62" t="inlineStr"/>
@@ -7503,37 +7141,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>115983187</v>
+        <v>115983103</v>
       </c>
       <c r="B63" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80468</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7543,10 +7176,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>532329</v>
+        <v>532279</v>
       </c>
       <c r="R63" t="n">
-        <v>7238371</v>
+        <v>7238500</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -7592,7 +7225,7 @@
       </c>
       <c r="AR63" t="inlineStr">
         <is>
-          <t>5497</t>
+          <t>5493</t>
         </is>
       </c>
       <c r="AT63" t="inlineStr"/>
@@ -7603,7 +7236,7 @@
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Robin Karlsson</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr">
@@ -7614,37 +7247,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>115983278</v>
+        <v>115983116</v>
       </c>
       <c r="B64" t="n">
-        <v>74647</v>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80468</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6440</v>
+        <v>6464</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7654,10 +7282,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>532364</v>
+        <v>532258</v>
       </c>
       <c r="R64" t="n">
-        <v>7238306</v>
+        <v>7238473</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -7703,7 +7331,7 @@
       </c>
       <c r="AR64" t="inlineStr">
         <is>
-          <t>5547</t>
+          <t>5472</t>
         </is>
       </c>
       <c r="AT64" t="inlineStr"/>
@@ -7714,7 +7342,7 @@
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Robin Karlsson</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr">
@@ -7725,37 +7353,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>115983192</v>
+        <v>115983130</v>
       </c>
       <c r="B65" t="n">
-        <v>78589</v>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80468</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>864</v>
+        <v>6464</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7765,10 +7388,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>532306</v>
+        <v>532509</v>
       </c>
       <c r="R65" t="n">
-        <v>7238366</v>
+        <v>7238456</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -7814,7 +7437,7 @@
       </c>
       <c r="AR65" t="inlineStr">
         <is>
-          <t>5492</t>
+          <t>5558</t>
         </is>
       </c>
       <c r="AT65" t="inlineStr"/>
@@ -7825,7 +7448,7 @@
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Robin Karlsson</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr">
@@ -7836,15 +7459,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>115983254</v>
+        <v>115983141</v>
       </c>
       <c r="B66" t="n">
-        <v>94068</v>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80468</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7852,21 +7470,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>2809</v>
+        <v>6464</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7876,10 +7494,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>532594</v>
+        <v>532722</v>
       </c>
       <c r="R66" t="n">
-        <v>7238326</v>
+        <v>7238444</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -7925,7 +7543,7 @@
       </c>
       <c r="AR66" t="inlineStr">
         <is>
-          <t>5613</t>
+          <t>5660</t>
         </is>
       </c>
       <c r="AT66" t="inlineStr"/>
@@ -7936,7 +7554,7 @@
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Robin Karlsson</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr">
@@ -7947,50 +7565,50 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>115983143</v>
+        <v>115983137</v>
       </c>
       <c r="B67" t="n">
-        <v>79587</v>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Dikanäs - Kittelfjäll, Ås lm</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>532365</v>
+        <v>532259</v>
       </c>
       <c r="R67" t="n">
-        <v>7238443</v>
+        <v>7238450</v>
       </c>
       <c r="S67" t="n">
         <v>5</v>
@@ -8025,6 +7643,11 @@
           <t>2023-06-15</t>
         </is>
       </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>hackmärken</t>
+        </is>
+      </c>
       <c r="AD67" t="b">
         <v>0</v>
       </c>
@@ -8036,7 +7659,7 @@
       </c>
       <c r="AR67" t="inlineStr">
         <is>
-          <t>5506</t>
+          <t>5487</t>
         </is>
       </c>
       <c r="AT67" t="inlineStr"/>
@@ -8058,15 +7681,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>115983159</v>
+        <v>115983171</v>
       </c>
       <c r="B68" t="n">
-        <v>79559</v>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8074,34 +7692,39 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Dikanäs - Kittelfjäll, Ås lm</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>532516</v>
+        <v>532453</v>
       </c>
       <c r="R68" t="n">
-        <v>7238424</v>
+        <v>7238403</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -8136,6 +7759,11 @@
           <t>2023-06-15</t>
         </is>
       </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Hackade i gran</t>
+        </is>
+      </c>
       <c r="AD68" t="b">
         <v>0</v>
       </c>
@@ -8147,7 +7775,7 @@
       </c>
       <c r="AR68" t="inlineStr">
         <is>
-          <t>5561</t>
+          <t>5586</t>
         </is>
       </c>
       <c r="AT68" t="inlineStr"/>
@@ -8158,7 +7786,7 @@
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Robin Karlsson</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr">
@@ -8169,15 +7797,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>115983178</v>
+        <v>115983181</v>
       </c>
       <c r="B69" t="n">
-        <v>77463</v>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8185,34 +7808,39 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>314</v>
+        <v>100109</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Dikanäs - Kittelfjäll, Ås lm</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>532442</v>
+        <v>532433</v>
       </c>
       <c r="R69" t="n">
-        <v>7238385</v>
+        <v>7238380</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -8247,6 +7875,11 @@
           <t>2023-06-15</t>
         </is>
       </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Hackade i gran</t>
+        </is>
+      </c>
       <c r="AD69" t="b">
         <v>0</v>
       </c>
@@ -8258,7 +7891,7 @@
       </c>
       <c r="AR69" t="inlineStr">
         <is>
-          <t>5584</t>
+          <t>5580</t>
         </is>
       </c>
       <c r="AT69" t="inlineStr"/>
@@ -8280,15 +7913,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>115983250</v>
+        <v>115983234</v>
       </c>
       <c r="B70" t="n">
-        <v>90359</v>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8296,34 +7924,39 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Dikanäs - Kittelfjäll, Ås lm</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>532372</v>
+        <v>532407</v>
       </c>
       <c r="R70" t="n">
-        <v>7238331</v>
+        <v>7238340</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -8358,6 +7991,11 @@
           <t>2023-06-15</t>
         </is>
       </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Hackade hål</t>
+        </is>
+      </c>
       <c r="AD70" t="b">
         <v>0</v>
       </c>
@@ -8369,7 +8007,7 @@
       </c>
       <c r="AR70" t="inlineStr">
         <is>
-          <t>5520</t>
+          <t>5566</t>
         </is>
       </c>
       <c r="AT70" t="inlineStr"/>
@@ -8391,50 +8029,54 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>115983221</v>
+        <v>115983109</v>
       </c>
       <c r="B71" t="n">
-        <v>74647</v>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58439</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6440</v>
+        <v>103018</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr"/>
+          <t>(Pallas, 1764)</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Dikanäs - Kittelfjäll, Ås lm</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>532353</v>
+        <v>532741</v>
       </c>
       <c r="R71" t="n">
-        <v>7238344</v>
+        <v>7238486</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -8480,7 +8122,7 @@
       </c>
       <c r="AR71" t="inlineStr">
         <is>
-          <t>5515</t>
+          <t>5633</t>
         </is>
       </c>
       <c r="AT71" t="inlineStr"/>
@@ -8491,7 +8133,7 @@
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Robin Karlsson</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr">
@@ -8502,15 +8144,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>115983147</v>
+        <v>115983166</v>
       </c>
       <c r="B72" t="n">
-        <v>82248</v>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8518,34 +8155,42 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>1312</v>
+        <v>103021</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Dikanäs - Kittelfjäll, Ås lm</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>532721</v>
+        <v>532284</v>
       </c>
       <c r="R72" t="n">
-        <v>7238441</v>
+        <v>7238417</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -8591,7 +8236,7 @@
       </c>
       <c r="AR72" t="inlineStr">
         <is>
-          <t>5659</t>
+          <t>5502</t>
         </is>
       </c>
       <c r="AT72" t="inlineStr"/>
@@ -8613,15 +8258,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>115983124</v>
+        <v>115983247</v>
       </c>
       <c r="B73" t="n">
-        <v>74647</v>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8629,21 +8269,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6440</v>
+        <v>103021</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8653,10 +8293,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>532458</v>
+        <v>532240</v>
       </c>
       <c r="R73" t="n">
-        <v>7238467</v>
+        <v>7238333</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -8702,7 +8342,7 @@
       </c>
       <c r="AR73" t="inlineStr">
         <is>
-          <t>5542</t>
+          <t>5486</t>
         </is>
       </c>
       <c r="AT73" t="inlineStr"/>
@@ -8713,7 +8353,7 @@
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Robin Karlsson</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr">
@@ -8724,15 +8364,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>115983176</v>
+        <v>115983224</v>
       </c>
       <c r="B74" t="n">
-        <v>74647</v>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58057</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8740,34 +8375,38 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6440</v>
+        <v>103031</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Dikanäs - Kittelfjäll, Ås lm</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>532531</v>
+        <v>532684</v>
       </c>
       <c r="R74" t="n">
-        <v>7238388</v>
+        <v>7238343</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -8813,7 +8452,7 @@
       </c>
       <c r="AR74" t="inlineStr">
         <is>
-          <t>5579</t>
+          <t>5620</t>
         </is>
       </c>
       <c r="AT74" t="inlineStr"/>
@@ -8824,7 +8463,7 @@
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Robin Karlsson</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr">
@@ -8835,50 +8474,49 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>115983229</v>
+        <v>115983260</v>
       </c>
       <c r="B75" t="n">
-        <v>79593</v>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58057</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6463</v>
+        <v>103031</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P75" t="inlineStr">
         <is>
           <t>Dikanäs - Kittelfjäll, Ås lm</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>532748</v>
+        <v>532549</v>
       </c>
       <c r="R75" t="n">
-        <v>7238341</v>
+        <v>7238321</v>
       </c>
       <c r="S75" t="n">
         <v>5</v>
@@ -8924,7 +8562,7 @@
       </c>
       <c r="AR75" t="inlineStr">
         <is>
-          <t>5684</t>
+          <t>5608</t>
         </is>
       </c>
       <c r="AT75" t="inlineStr"/>
@@ -8935,7 +8573,7 @@
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Robin Karlsson</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr">
@@ -8946,15 +8584,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>115983166</v>
+        <v>115983265</v>
       </c>
       <c r="B76" t="n">
-        <v>57414</v>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58057</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8962,42 +8595,43 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>103021</v>
+        <v>103031</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr"/>
-      <c r="K76" t="inlineStr"/>
-      <c r="L76" t="inlineStr"/>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N76" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Dikanäs - Kittelfjäll, Ås lm</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>532284</v>
+        <v>532596</v>
       </c>
       <c r="R76" t="n">
-        <v>7238417</v>
+        <v>7238317</v>
       </c>
       <c r="S76" t="n">
         <v>5</v>
@@ -9043,7 +8677,7 @@
       </c>
       <c r="AR76" t="inlineStr">
         <is>
-          <t>5502</t>
+          <t>5607</t>
         </is>
       </c>
       <c r="AT76" t="inlineStr"/>
@@ -9065,15 +8699,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>115983156</v>
+        <v>115983263</v>
       </c>
       <c r="B77" t="n">
-        <v>79593</v>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9081,34 +8710,38 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6463</v>
+        <v>219790</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Dikanäs - Kittelfjäll, Ås lm</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>532400</v>
+        <v>532380</v>
       </c>
       <c r="R77" t="n">
-        <v>7238430</v>
+        <v>7238319</v>
       </c>
       <c r="S77" t="n">
         <v>5</v>
@@ -9154,7 +8787,7 @@
       </c>
       <c r="AR77" t="inlineStr">
         <is>
-          <t>5531</t>
+          <t>5543</t>
         </is>
       </c>
       <c r="AT77" t="inlineStr"/>
@@ -9165,7 +8798,7 @@
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Robin Karlsson</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr">
@@ -9176,15 +8809,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>115983253</v>
+        <v>115983167</v>
       </c>
       <c r="B78" t="n">
-        <v>79587</v>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99140</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9192,21 +8820,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6462</v>
+        <v>221952</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -9216,10 +8844,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>532388</v>
+        <v>532451</v>
       </c>
       <c r="R78" t="n">
-        <v>7238330</v>
+        <v>7238409</v>
       </c>
       <c r="S78" t="n">
         <v>5</v>
@@ -9265,7 +8893,7 @@
       </c>
       <c r="AR78" t="inlineStr">
         <is>
-          <t>5555</t>
+          <t>5593</t>
         </is>
       </c>
       <c r="AT78" t="inlineStr"/>
@@ -9276,10 +8904,646 @@
       </c>
       <c r="AX78" t="inlineStr">
         <is>
+          <t>Olle Kvarnbäck</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr">
+        <is>
+          <t>EEN0060 Hemavan - Kittelfjäll NVI</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>115983210</v>
+      </c>
+      <c r="B79" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Dikanäs - Kittelfjäll, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>532582</v>
+      </c>
+      <c r="R79" t="n">
+        <v>7238354</v>
+      </c>
+      <c r="S79" t="n">
+        <v>5</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2023-06-15</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2023-06-15</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AR79" t="inlineStr">
+        <is>
+          <t>5590</t>
+        </is>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Rickard Gustafsson</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Olle Kvarnbäck</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr">
+        <is>
+          <t>EEN0060 Hemavan - Kittelfjäll NVI</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>115983241</v>
+      </c>
+      <c r="B80" t="n">
+        <v>100143</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>222467</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Gräsull</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Eriophorum latifolium</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Hoppe</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Dikanäs - Kittelfjäll, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>532659</v>
+      </c>
+      <c r="R80" t="n">
+        <v>7238335</v>
+      </c>
+      <c r="S80" t="n">
+        <v>5</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2023-06-15</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2023-06-15</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AR80" t="inlineStr">
+        <is>
+          <t>5631</t>
+        </is>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Rickard Gustafsson</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
           <t>Robin Karlsson</t>
         </is>
       </c>
-      <c r="AY78" t="inlineStr">
+      <c r="AY80" t="inlineStr">
+        <is>
+          <t>EEN0060 Hemavan - Kittelfjäll NVI</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>115983146</v>
+      </c>
+      <c r="B81" t="n">
+        <v>80398</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>229748</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Gytterlav</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Protopannaria pezizoides</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Dikanäs - Kittelfjäll, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>532778</v>
+      </c>
+      <c r="R81" t="n">
+        <v>7238441</v>
+      </c>
+      <c r="S81" t="n">
+        <v>5</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2023-06-15</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2023-06-15</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AR81" t="inlineStr">
+        <is>
+          <t>5672</t>
+        </is>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Rickard Gustafsson</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Robin Karlsson</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr">
+        <is>
+          <t>EEN0060 Hemavan - Kittelfjäll NVI</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>115983223</v>
+      </c>
+      <c r="B82" t="n">
+        <v>80398</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>229748</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Gytterlav</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Protopannaria pezizoides</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Dikanäs - Kittelfjäll, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>532755</v>
+      </c>
+      <c r="R82" t="n">
+        <v>7238343</v>
+      </c>
+      <c r="S82" t="n">
+        <v>5</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2023-06-15</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2023-06-15</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AR82" t="inlineStr">
+        <is>
+          <t>5680</t>
+        </is>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Rickard Gustafsson</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>Olle Kvarnbäck</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr">
+        <is>
+          <t>EEN0060 Hemavan - Kittelfjäll NVI</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>115983107</v>
+      </c>
+      <c r="B83" t="n">
+        <v>95765</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>1004672</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Källmossor</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Philonotis</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Brid.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Dikanäs - Kittelfjäll, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>532686</v>
+      </c>
+      <c r="R83" t="n">
+        <v>7238492</v>
+      </c>
+      <c r="S83" t="n">
+        <v>5</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>2023-06-15</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>2023-06-15</t>
+        </is>
+      </c>
+      <c r="AD83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AR83" t="inlineStr">
+        <is>
+          <t>5632</t>
+        </is>
+      </c>
+      <c r="AT83" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Rickard Gustafsson</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>Robin Karlsson</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr">
+        <is>
+          <t>EEN0060 Hemavan - Kittelfjäll NVI</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>115983151</v>
+      </c>
+      <c r="B84" t="n">
+        <v>95765</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>1004672</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Källmossor</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Philonotis</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Brid.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Dikanäs - Kittelfjäll, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q84" t="n">
+        <v>532787</v>
+      </c>
+      <c r="R84" t="n">
+        <v>7238435</v>
+      </c>
+      <c r="S84" t="n">
+        <v>5</v>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>2023-06-15</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>2023-06-15</t>
+        </is>
+      </c>
+      <c r="AD84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AR84" t="inlineStr">
+        <is>
+          <t>5677</t>
+        </is>
+      </c>
+      <c r="AT84" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>Rickard Gustafsson</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>Olle Kvarnbäck</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr">
         <is>
           <t>EEN0060 Hemavan - Kittelfjäll NVI</t>
         </is>
